--- a/ARM Functions/Other Mechanics/Starters 50% shiny.xlsx
+++ b/ARM Functions/Other Mechanics/Starters 50% shiny.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1945C428-E9D3-4C2E-9A52-848846B342B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA49449-34E3-4DF8-BE88-7954ABB57378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Edited main" sheetId="6" r:id="rId1"/>
     <sheet name="original" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="84">
   <si>
     <t>Address</t>
   </si>
@@ -237,15 +237,9 @@
     <t>fail</t>
   </si>
   <si>
-    <t>005B9F5C</t>
-  </si>
-  <si>
     <t>Alolan Starters 50% shiny</t>
   </si>
   <si>
-    <t>B899F50A</t>
-  </si>
-  <si>
     <t>B801D4E1</t>
   </si>
   <si>
@@ -261,15 +255,9 @@
     <t>D8005013</t>
   </si>
   <si>
-    <t>9599F5EA</t>
-  </si>
-  <si>
     <t>0200A0E3</t>
   </si>
   <si>
-    <t>FC9BF6EB</t>
-  </si>
-  <si>
     <t>010050E3</t>
   </si>
   <si>
@@ -280,6 +268,27 @@
   </si>
   <si>
     <t>62660AEA</t>
+  </si>
+  <si>
+    <t>push {r0, r1, r2}</t>
+  </si>
+  <si>
+    <t>005B9F54</t>
+  </si>
+  <si>
+    <t>BA99F50A</t>
+  </si>
+  <si>
+    <t>07002DE9</t>
+  </si>
+  <si>
+    <t>9699F5EA</t>
+  </si>
+  <si>
+    <t>FD9BF6EB</t>
+  </si>
+  <si>
+    <t>0700BDE8</t>
   </si>
 </sst>
 </file>
@@ -347,12 +356,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="11.5" style="4" bestFit="1" customWidth="1"/>
@@ -725,36 +734,36 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>_xlfn.CONCAT("b 0x",A12)</f>
-        <v>b 0x005B9F5C</v>
+        <v>b 0x005B9F54</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>_xlfn.CONCAT("b 0x",E12)</f>
-        <v>b 0x005B9F5C</v>
+        <v>b 0x005B9F54</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -772,7 +781,7 @@
         <v>46</v>
       </c>
       <c r="E4" s="4" t="str">
-        <f t="shared" ref="E4:F4" si="1">DEC2HEX(HEX2DEC(E3)+4,8)</f>
+        <f t="shared" ref="E4" si="1">DEC2HEX(HEX2DEC(E3)+4,8)</f>
         <v>003205D0</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -783,43 +792,43 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7" hidden="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -828,7 +837,7 @@
       <c r="E9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -836,26 +845,26 @@
       </c>
     </row>
     <row r="10" spans="1:7" hidden="1">
-      <c r="B10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="B10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="A11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="str">
         <f>_xlfn.CONCAT("beq 0x",A6)</f>
@@ -865,10 +874,10 @@
         <v>58</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>_xlfn.CONCAT("beq 0x",E6)</f>
@@ -877,275 +886,321 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="str">
-        <f t="shared" ref="A13:A23" si="2">DEC2HEX(HEX2DEC(A12)+4,8)</f>
-        <v>005B9F60</v>
+        <f t="shared" ref="A13:A25" si="2">DEC2HEX(HEX2DEC(A12)+4,8)</f>
+        <v>005B9F58</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f t="shared" ref="E13:E23" si="3">DEC2HEX(HEX2DEC(E12)+4,8)</f>
-        <v>005B9F60</v>
+        <f t="shared" ref="E13:E25" si="3">DEC2HEX(HEX2DEC(E12)+4,8)</f>
+        <v>005B9F58</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F64</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>70</v>
+        <v>005B9F5C</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="E14" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F64</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>70</v>
+        <v>005B9F5C</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F68</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>005B9F60</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="E15" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F68</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>71</v>
+        <v>005B9F60</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F6C</v>
+        <v>005B9F64</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E16" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F6C</v>
+        <v>005B9F64</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F70</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>73</v>
+        <v>005B9F68</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F70</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>73</v>
+        <v>005B9F68</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F74</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="4" t="str">
-        <f>C23</f>
-        <v>b 0x003205D0</v>
+        <v>005B9F6C</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F74</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f>G23</f>
-        <v>b 0x003205D0</v>
+        <v>005B9F6C</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F78</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>005B9F70</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="4" t="str">
+        <f>C25</f>
+        <v>b 0x003205D0</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="E19" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F78</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>60</v>
+        <v>005B9F70</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="4" t="str">
+        <f>G25</f>
+        <v>b 0x003205D0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F7C</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>76</v>
+        <v>005B9F74</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E20" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F7C</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>76</v>
+        <v>005B9F74</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F80</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>77</v>
+        <v>005B9F78</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="E21" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F80</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>77</v>
+        <v>005B9F78</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>005B9F84</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="4" t="str">
-        <f>C12</f>
-        <v>beq 0x00320644</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>64</v>
+        <v>005B9F7C</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E22" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>005B9F84</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f>G12</f>
-        <v>beq 0x00320644</v>
+        <v>005B9F7C</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="str">
         <f t="shared" si="2"/>
+        <v>005B9F80</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="str">
+        <f>SUBSTITUTE(C13,"push","pop")</f>
+        <v>pop {r0, r1, r2}</v>
+      </c>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>005B9F80</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="4" t="str">
+        <f>SUBSTITUTE(G13,"push","pop")</f>
+        <v>pop {r0, r1, r2}</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>005B9F84</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="4" t="str">
+        <f>C12</f>
+        <v>beq 0x00320644</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>005B9F84</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="4" t="str">
+        <f>G12</f>
+        <v>beq 0x00320644</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="str">
+        <f t="shared" si="2"/>
         <v>005B9F88</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="4" t="str">
+      <c r="B25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="4" t="str">
         <f>_xlfn.CONCAT("b 0x",A4)</f>
         <v>b 0x003205D0</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="4" t="str">
+      <c r="E25" s="4" t="str">
         <f t="shared" si="3"/>
         <v>005B9F88</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="4" t="str">
+      <c r="F25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="4" t="str">
         <f>_xlfn.CONCAT("b 0x",E4)</f>
         <v>b 0x003205D0</v>
       </c>
